--- a/readme_file_information.xlsx
+++ b/readme_file_information.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleaw\Documents\PhD Fall 2021 - Spring 2022\dissertation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348EBA93-C71A-42BB-820D-CCB19BA08BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{037D94DF-3269-4900-88AE-35970BA87593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15840" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{CBBF95AB-F81E-4FC2-8BBB-B7D3AC8BC92D}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{CBBF95AB-F81E-4FC2-8BBB-B7D3AC8BC92D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Files" sheetId="2" r:id="rId1"/>
+    <sheet name="Outputs" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="172">
   <si>
     <t>File</t>
   </si>
@@ -68,9 +69,6 @@
     <t>Join Flood Factor risk scores (2019 snapshot) to Cook County parcel universe</t>
   </si>
   <si>
-    <t>data/raw/floodfactor_scores.csv</t>
-  </si>
-  <si>
     <t>shapefile_sfha_changes.R</t>
   </si>
   <si>
@@ -89,9 +87,6 @@
     <t>None</t>
   </si>
   <si>
-    <t>Takes damagedCity variable from Open FEMA individual assistance, exports city names which had tons of typos. This was put in chatGPT to match with clean names</t>
-  </si>
-  <si>
     <t>Exploratory &amp; Descriptive Analysis</t>
   </si>
   <si>
@@ -183,9 +178,6 @@
   </si>
   <si>
     <t>Analysis Step</t>
-  </si>
-  <si>
-    <t>ADD</t>
   </si>
   <si>
     <r>
@@ -247,7 +239,7 @@
   </si>
   <si>
     <r>
-      <t>data/raw/ia.city_names.csv</t>
+      <t>data/raw/nfippolicies_CookCounty_all.csv</t>
     </r>
     <r>
       <rPr>
@@ -255,7 +247,7 @@
         <rFont val="Times New Roman"/>
         <family val="2"/>
       </rPr>
-      <t> which becomes </t>
+      <t>, </t>
     </r>
     <r>
       <rPr>
@@ -263,12 +255,12 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>data/processed/City_Mapping_Names.csv</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>data/raw/nfippolicies_CookCounty_all.csv</t>
+      <t>data/raw/nfipclaims_CookCounty.csv</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>data/raw/indiv_assistance_CookCounty.csv</t>
     </r>
     <r>
       <rPr>
@@ -284,12 +276,28 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>data/raw/nfipclaims_CookCounty.csv</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>data/raw/indiv_assistance_CookCounty.csv</t>
+      <t>data/processed/treated_zipcodes.csv</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Illinois Buyout Database </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.75"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>BuyoutPoints_Statewide.xlsx</t>
+    </r>
+  </si>
+  <si>
+    <t>mcmillen_salescomparison.qmd</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Flood_Appeal_PINs.qmd - </t>
     </r>
     <r>
       <rPr>
@@ -297,7 +305,92 @@
         <rFont val="Times New Roman"/>
         <family val="2"/>
       </rPr>
-      <t>, </t>
+      <t>ARCHIVED</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Flood_factor_pins.qmd - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+      </rPr>
+      <t>ARCHIVED</t>
+    </r>
+  </si>
+  <si>
+    <t>singlefamily_assessed_values.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">res_pins_ever.csv, sfha_indicator_pins.csv, Assessor_Parcel_Sales.csv, parcels_wFIRMs.csv, floodfactor_scores.csv </t>
+  </si>
+  <si>
+    <t>singlefamily_assessed_values.csv, treated.csv</t>
+  </si>
+  <si>
+    <t>Naïve OLS and FE models using the "easy" PINs that were always residential</t>
+  </si>
+  <si>
+    <t>reads in McMillens Sales Data</t>
+  </si>
+  <si>
+    <t>parquet file from McMillen, Assessor_sales file from CCAO</t>
+  </si>
+  <si>
+    <t>AssessedValues _andFIRMS.qmd</t>
+  </si>
+  <si>
+    <t>descriptive_stats _singlefam.qmd</t>
+  </si>
+  <si>
+    <t>Cook_flood_policies _and_claims.qmd</t>
+  </si>
+  <si>
+    <t>CC_Individual_ FEMA_Assistance.qmd</t>
+  </si>
+  <si>
+    <t>pull_NFIP_ redactedclaims.R</t>
+  </si>
+  <si>
+    <t>pull_individual_ assistance_applicants.R</t>
+  </si>
+  <si>
+    <t>clean_damanged City_names</t>
+  </si>
+  <si>
+    <t>detect_flood_variable _change_in_CCAO</t>
+  </si>
+  <si>
+    <t>pull_floodfactor _pin_list.R</t>
+  </si>
+  <si>
+    <t>pull_distinct_ resPINs.R</t>
+  </si>
+  <si>
+    <r>
+      <t>CookCounty _ParcelMaps.qmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+      </rPr>
+      <t> - ARCHIVED</t>
+    </r>
+  </si>
+  <si>
+    <t>Parcel universe with PINs, Flood Factor data</t>
+  </si>
+  <si>
+    <t>NFHL 2018 and NFHL 2024 (NFHL_17_20180129.gdb, Statewide_NFHL_17_20240628.gdb)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">data/raw/indiv_assistance_CookCounty.csv, </t>
     </r>
     <r>
       <rPr>
@@ -310,7 +403,7 @@
   </si>
   <si>
     <r>
-      <t>Illinois Buyout Database </t>
+      <t xml:space="preserve">data/raw/nfipclaims_CookCounty.csv, </t>
     </r>
     <r>
       <rPr>
@@ -318,15 +411,12 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>BuyoutPoints_Statewide.xlsx</t>
-    </r>
-  </si>
-  <si>
-    <t>mcmillen_salescomparison.qmd</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Flood_Appeal_PINs.qmd - </t>
+      <t>data/raw/nfippolicies_CookCounty_all.csv</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>data/raw/assessor_parcel_sales.csv</t>
     </r>
     <r>
       <rPr>
@@ -334,12 +424,15 @@
         <rFont val="Times New Roman"/>
         <family val="2"/>
       </rPr>
-      <t>ARCHIVED</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Flood_factor_pins.qmd - </t>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.75"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>parcels_sfha_2018.gpkg</t>
     </r>
     <r>
       <rPr>
@@ -347,63 +440,15 @@
         <rFont val="Times New Roman"/>
         <family val="2"/>
       </rPr>
-      <t>ARCHIVED</t>
-    </r>
-  </si>
-  <si>
-    <t>singlefamily_assessed_values.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">res_pins_ever.csv, sfha_indicator_pins.csv, Assessor_Parcel_Sales.csv, parcels_wFIRMs.csv, floodfactor_scores.csv </t>
-  </si>
-  <si>
-    <t>singlefamily_assessed_values.csv, treated.csv</t>
-  </si>
-  <si>
-    <t>Combine files created by scripts. Combine data necessary for creating variables in models.</t>
-  </si>
-  <si>
-    <t>Naïve OLS and FE models using the "easy" PINs that were always residential</t>
-  </si>
-  <si>
-    <t>reads in McMillens Sales Data</t>
-  </si>
-  <si>
-    <t>parquet file from McMillen, Assessor_sales file from CCAO</t>
-  </si>
-  <si>
-    <t>AssessedValues _andFIRMS.qmd</t>
-  </si>
-  <si>
-    <t>descriptive_stats _singlefam.qmd</t>
-  </si>
-  <si>
-    <t>Cook_flood_policies _and_claims.qmd</t>
-  </si>
-  <si>
-    <t>CC_Individual_ FEMA_Assistance.qmd</t>
-  </si>
-  <si>
-    <t>pull_NFIP_ redactedclaims.R</t>
-  </si>
-  <si>
-    <t>pull_individual_ assistance_applicants.R</t>
-  </si>
-  <si>
-    <t>clean_damanged City_names</t>
-  </si>
-  <si>
-    <t>detect_flood_variable _change_in_CCAO</t>
-  </si>
-  <si>
-    <t>pull_floodfactor _pin_list.R</t>
-  </si>
-  <si>
-    <t>pull_distinct_ resPINs.R</t>
-  </si>
-  <si>
-    <r>
-      <t>AssessedValue _ExploratoryGraphs.rmd -</t>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.75"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>parcels_sfha_2024.gpkg</t>
     </r>
     <r>
       <rPr>
@@ -411,12 +456,15 @@
         <rFont val="Times New Roman"/>
         <family val="2"/>
       </rPr>
-      <t> ARCHIVED</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CookCounty _ParcelMaps.qmd</t>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.75"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>parcels_lomrs.gpkg</t>
     </r>
     <r>
       <rPr>
@@ -424,18 +472,7 @@
         <rFont val="Times New Roman"/>
         <family val="2"/>
       </rPr>
-      <t> - ARCHIVED</t>
-    </r>
-  </si>
-  <si>
-    <t>Parcel universe with PINs, Flood Factor data</t>
-  </si>
-  <si>
-    <t>NFHL 2018 and NFHL 2024 (NFHL_17_20180129.gdb, Statewide_NFHL_17_20240628.gdb)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">data/raw/indiv_assistance_CookCounty.csv, </t>
+      <t>, </t>
     </r>
     <r>
       <rPr>
@@ -443,12 +480,277 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>data/processed/treated_zipcodes.csv</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">data/raw/nfipclaims_CookCounty.csv, </t>
+      <t>data/raw/pins_floodfactor_2019.csv</t>
+    </r>
+  </si>
+  <si>
+    <t>bulding_footprint_clips.R</t>
+  </si>
+  <si>
+    <t>cook_MS.shp (building outlines), SFHA shapefiles</t>
+  </si>
+  <si>
+    <t>Identifies parcels that have a building in them where the building is within the SFHA. Specifically uses premade SFHA parcels and intersects it with building outlines to see which SFHA parcels to keep. (earlier SFHA parcel files were created from the land polygon intersecting with the SFHA and was over inclusive.)</t>
+  </si>
+  <si>
+    <t>processed/buildings_in_sfha_w_parcelinfo.shp, processed/buildings_distinct_in_sfha.csv</t>
+  </si>
+  <si>
+    <t>Used to assign municipality names to individual aid data from FEMA that had typos in names. Join to IA data. Takes damagedCity variable from Open FEMA individual assistance, exports city names which had tons of typos. This was put in chatGPT to match with clean names.</t>
+  </si>
+  <si>
+    <t>data_prep.R</t>
+  </si>
+  <si>
+    <t>raw/Assessor_Parcel_Sales_20250105.csv, processed/parcels_wFIRMS.csv,
+processed/sfha_indicator_pins.csv,
+processed/lomr_pins_2024.csv</t>
+  </si>
+  <si>
+    <t>sales_prepped.rds, res_sales.rds</t>
+  </si>
+  <si>
+    <t>pull_addresses_pins_wo_ffscores.R</t>
+  </si>
+  <si>
+    <t>Takes PINs that didn't have flood factor scores and pulls addresses to make searching flood factor score faster. Otherwise you have to search the PIN to get the address, and then search the address to get the Risk Score.</t>
+  </si>
+  <si>
+    <t>missing_floodfactor_scores.xlsx, API for Cook County parcel addresses</t>
+  </si>
+  <si>
+    <t>pins_with_some_addresses.csv</t>
+  </si>
+  <si>
+    <t>waterbasins_map.R</t>
+  </si>
+  <si>
+    <t>Makes visualization of cook county with rivers and water basins. Not actually used for dissertation.</t>
+  </si>
+  <si>
+    <t>Water Basins shapefiles online. River shapefiles</t>
+  </si>
+  <si>
+    <t>2_create_datasets.qmd</t>
+  </si>
+  <si>
+    <t>3_check_assumptions</t>
+  </si>
+  <si>
+    <t>Question1</t>
+  </si>
+  <si>
+    <t>Question2</t>
+  </si>
+  <si>
+    <t>Question3</t>
+  </si>
+  <si>
+    <t>city_name_mapping.csv, FEMA API for individual assistance</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t>Created By</t>
+  </si>
+  <si>
+    <t>pull_NFIP_redactedclaims.R</t>
+  </si>
+  <si>
+    <t>pull_individual_assistance_applicants.R</t>
+  </si>
+  <si>
+    <t>pull_distinct_resPINs.R</t>
+  </si>
+  <si>
+    <t>pull_floodfactor_pin_list.R</t>
+  </si>
+  <si>
+    <t>??</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>ia_city_names.csv</t>
+  </si>
+  <si>
+    <t>File Path</t>
+  </si>
+  <si>
+    <t>data/raw/</t>
+  </si>
+  <si>
+    <t>data/processed/</t>
+  </si>
+  <si>
+    <t>parcels_2018.gpkg</t>
+  </si>
+  <si>
+    <t>parcels_2023.gpkg</t>
+  </si>
+  <si>
+    <t>nfippolicies_CookCounty_all.csv</t>
+  </si>
+  <si>
+    <t>nfipclaims_CookCounty.csv</t>
+  </si>
+  <si>
+    <t>residential_pins_ever.csv</t>
+  </si>
+  <si>
+    <t>pin_muni_key.csv</t>
+  </si>
+  <si>
+    <t>muniname_taxcode_key.csv</t>
+  </si>
+  <si>
+    <t>floodfactor_scores.csv</t>
+  </si>
+  <si>
+    <t>treated.csv</t>
+  </si>
+  <si>
+    <t>indiv_assistance_V2_CookCounty.csv</t>
+  </si>
+  <si>
+    <t>nfip_policies_IL.csv</t>
+  </si>
+  <si>
+    <t>parcel_universe_currentyear.csv</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>s_FIRM_PAN.csv</t>
+  </si>
+  <si>
+    <t>buildings_distinct_in_sfha</t>
+  </si>
+  <si>
+    <t>City_Name_Mapping.csv</t>
+  </si>
+  <si>
+    <t>chat gpt helped make from messy city names in FEMA data.</t>
+  </si>
+  <si>
+    <t>df_pairs.RDS</t>
+  </si>
+  <si>
+    <t>ff_pairs.RDS</t>
+  </si>
+  <si>
+    <t>df_prep.RDS</t>
+  </si>
+  <si>
+    <t>joined_LOMR_parcels.csv</t>
+  </si>
+  <si>
+    <t>joined_LOMR_parcels_from_arcgis.csv</t>
+  </si>
+  <si>
+    <t>lomr_pins_2024.csv</t>
+  </si>
+  <si>
+    <t>missing_floodfactor_scores.csv</t>
+  </si>
+  <si>
+    <t>parcels_wFIRMS.csv</t>
+  </si>
+  <si>
+    <t>res_sales.rds</t>
+  </si>
+  <si>
+    <t>sales_prepped.rds</t>
+  </si>
+  <si>
+    <t>sfha_indicator_parcels.csv</t>
+  </si>
+  <si>
+    <t>sfha_indicator_pins.csv</t>
+  </si>
+  <si>
+    <t>treated_census_blocks</t>
+  </si>
+  <si>
+    <t>treated_zipcodes.csv</t>
+  </si>
+  <si>
+    <t>IA file</t>
+  </si>
+  <si>
+    <t>Delete?</t>
+  </si>
+  <si>
+    <t>housing_assistance_owners.csv</t>
+  </si>
+  <si>
+    <t>FEMA File Download</t>
+  </si>
+  <si>
+    <t>inputs</t>
+  </si>
+  <si>
+    <t>outputs/</t>
+  </si>
+  <si>
+    <t>nbh_pins_parceluniversepull2022.csv</t>
+  </si>
+  <si>
+    <t>pins_in_Blocks_2006_2023_20241126.csv</t>
+  </si>
+  <si>
+    <t>clean_damanged City_names.r</t>
+  </si>
+  <si>
+    <t>data as it comes from Cook Parcel Universe API</t>
+  </si>
+  <si>
+    <t>attempts to fill in missing zipcodes and geographic variables based on shared land blocks or having a zipcode or assessor neighborhood associated with a municipality, zipcode, etc.</t>
+  </si>
+  <si>
+    <t>data/raw/floodfactor_scores.csv, data/processed/floodfactor_scores.csv</t>
+  </si>
+  <si>
+    <t>arcgis</t>
+  </si>
+  <si>
+    <t>res_sales.rds, pin_muni_key.csv, muni_shortnames.xlsx</t>
+  </si>
+  <si>
+    <t>df_pairs.RDS, ff_pairs.RDS, df_prep.RDS</t>
+  </si>
+  <si>
+    <t>Creates df_prep and df_pairs for files that run the models. Reads in sales data and turns it into repeat sales data format</t>
+  </si>
+  <si>
+    <t>Takes sales data and joins FIRM variables and SFHA indicator variables to the sales. Makes the res_sales.RDS file that goes to 2_create_dataframes which creates the  dataframes for files that run models (Question1, Question2, Question3)</t>
+  </si>
+  <si>
+    <t>building_footprint_clips.R</t>
+  </si>
+  <si>
+    <t>Check for parallel trends for models</t>
+  </si>
+  <si>
+    <t>indiv_assistance_V2_CookCounty_wNames.csv</t>
+  </si>
+  <si>
+    <t>Open FEMA API, City_Name_Mapping.csv</t>
+  </si>
+  <si>
+    <r>
+      <t>data/raw/ia_city_names.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <rFont val="Times New Roman"/>
+        <family val="2"/>
+      </rPr>
+      <t> which becomes </t>
     </r>
     <r>
       <rPr>
@@ -456,84 +758,42 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>data/raw/nfippolicies_CookCounty_all.csv</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>data/raw/assessor_parcel_sales.csv</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <rFont val="Times New Roman"/>
-        <family val="2"/>
-      </rPr>
-      <t>, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.75"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>parcels_sfha_2018.gpkg</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <rFont val="Times New Roman"/>
-        <family val="2"/>
-      </rPr>
-      <t>, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.75"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>parcels_sfha_2024.gpkg</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <rFont val="Times New Roman"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.75"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>parcels_lomrs.gpkg</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <rFont val="Times New Roman"/>
-        <family val="2"/>
-      </rPr>
-      <t>, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.75"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>data/raw/pins_floodfactor_2019.csv</t>
-    </r>
+      <t>data/processed/City_Mapping_Names.csv, indiv_assistance_V2_CookCounty_wNames.csv</t>
+    </r>
+  </si>
+  <si>
+    <t>DV Model Type</t>
+  </si>
+  <si>
+    <t>Assessed Value</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Combine files created by scripts. Combine data necessary for creating variables in models. Code for combining files was rough draft for creating data_prep.R script</t>
+  </si>
+  <si>
+    <t>data_prep_buildings.R</t>
+  </si>
+  <si>
+    <t>didFF_test.R</t>
+  </si>
+  <si>
+    <t>df_prep_buildings.RDS</t>
+  </si>
+  <si>
+    <t>outputs/didFF_model_out.rds, outputs/didFF_plot_out.rds, outputs/didFF_model_out2.rds, outputs/didFF_plot_out2.rds</t>
+  </si>
+  <si>
+    <t>Implied density tests of distributional parallel trends. Saves model and plot output because it takes a long time to run.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="18"/>
       <color theme="1"/>
@@ -568,6 +828,25 @@
       <name val="Times New Roman"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF212529"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF7D12BA"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF212529"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -595,7 +874,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -612,11 +891,173 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="11">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF212529"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF212529"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF212529"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF212529"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF212529"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF212529"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -665,16 +1106,36 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FEF62D60-AD25-4B9B-92F2-6BD027E8C017}" name="Table2" displayName="Table2" ref="A1:E21" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="A1:E21" xr:uid="{FEF62D60-AD25-4B9B-92F2-6BD027E8C017}"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FEF62D60-AD25-4B9B-92F2-6BD027E8C017}" name="Table2" displayName="Table2" ref="A1:F31" totalsRowShown="0" headerRowDxfId="10">
+  <autoFilter ref="A1:F31" xr:uid="{FEF62D60-AD25-4B9B-92F2-6BD027E8C017}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E23">
+    <sortCondition ref="A1:A23"/>
+  </sortState>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{67B093ED-B042-42AF-828B-0E3979AEE20D}" name="File"/>
-    <tableColumn id="2" xr3:uid="{2469F763-8CD9-4F9B-81C9-081F0416F7A5}" name="Purpose" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{43956458-8468-4B36-9A02-0003207D1AF5}" name="Inputs" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{7920B79F-C2A1-4A94-A4C1-4C2F4CD3CC3B}" name="Outputs" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{2469F763-8CD9-4F9B-81C9-081F0416F7A5}" name="Purpose" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{43956458-8468-4B36-9A02-0003207D1AF5}" name="Inputs" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{7920B79F-C2A1-4A94-A4C1-4C2F4CD3CC3B}" name="Outputs" dataDxfId="7"/>
     <tableColumn id="5" xr3:uid="{8998AB64-C713-4A46-ACAB-BE6621288648}" name="Analysis Step"/>
+    <tableColumn id="6" xr3:uid="{235814BD-1B80-4B94-B701-26874451ABA9}" name="DV Model Type" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{59E3DA47-3C97-48AE-8BE5-10905542AA94}" name="Table3" displayName="Table3" ref="A1:D38" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:D38" xr:uid="{59E3DA47-3C97-48AE-8BE5-10905542AA94}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C34">
+    <sortCondition ref="B1:B34"/>
+  </sortState>
+  <tableColumns count="4">
+    <tableColumn id="3" xr3:uid="{AC962285-503A-4963-A003-05FA381B10C7}" name="File Path" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{B777D240-3778-451E-A05B-8D2528E4BD53}" name="Output" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{168B95B9-E677-4740-9CB5-0E8DE4E5D63D}" name="Created By" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{BCBBA88B-69AC-4622-A217-558B80AFF3B1}" name="Column1" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -995,7 +1456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F477E64-1C4D-4E5A-ADA3-AF3D9C88449B}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultColWidth="23" defaultRowHeight="23.1" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="1" width="28.86328125" style="4" customWidth="1"/>
@@ -1006,7 +1467,7 @@
     <col min="6" max="16384" width="23" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1020,339 +1481,946 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="90" x14ac:dyDescent="0.8">
+        <v>46</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="46.2" x14ac:dyDescent="0.8">
       <c r="A2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="161.69999999999999" x14ac:dyDescent="0.8">
+      <c r="A3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="66.900000000000006" x14ac:dyDescent="0.8">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.8">
+      <c r="A5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="138.6" x14ac:dyDescent="0.8">
+      <c r="A6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="138.6" x14ac:dyDescent="0.8">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="46.2" x14ac:dyDescent="0.8">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="46.2" x14ac:dyDescent="0.8">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="138.6" x14ac:dyDescent="0.8">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="69.3" x14ac:dyDescent="0.8">
-      <c r="A6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="D7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
         <v>16</v>
       </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="92.4" x14ac:dyDescent="0.8">
-      <c r="A7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="66.900000000000006" x14ac:dyDescent="0.8">
+    </row>
+    <row r="8" spans="1:6" ht="113.1" x14ac:dyDescent="0.8">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="87" x14ac:dyDescent="0.8">
+        <v>16</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="46.2" x14ac:dyDescent="0.8">
       <c r="A9" t="s">
         <v>71</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="66.900000000000006" x14ac:dyDescent="0.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="115.5" x14ac:dyDescent="0.8">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>33</v>
+        <v>157</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="46.2" x14ac:dyDescent="0.8">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="87" x14ac:dyDescent="0.8">
-      <c r="A11" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="E11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="138.6" x14ac:dyDescent="0.8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="69.3" x14ac:dyDescent="0.8">
       <c r="A12" t="s">
         <v>68</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="113.1" x14ac:dyDescent="0.8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="69.3" x14ac:dyDescent="0.8">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="69.3" x14ac:dyDescent="0.8">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="115.5" x14ac:dyDescent="0.8">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="F15" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="46.2" x14ac:dyDescent="0.8">
+      <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="115.5" x14ac:dyDescent="0.8">
+      <c r="A17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="66.900000000000006" x14ac:dyDescent="0.8">
+      <c r="A18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="69.3" x14ac:dyDescent="0.8">
+      <c r="A19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="66.900000000000006" x14ac:dyDescent="0.8">
+      <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="66.900000000000006" x14ac:dyDescent="0.8">
+      <c r="A21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="46.2" x14ac:dyDescent="0.8">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="138.6" x14ac:dyDescent="0.8">
+      <c r="A23" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="46.2" x14ac:dyDescent="0.8">
+      <c r="A24" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="69.3" x14ac:dyDescent="0.8">
+      <c r="A25" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.8">
+      <c r="A26" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.8">
+      <c r="A27" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.8">
+      <c r="A28" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="46.2" x14ac:dyDescent="0.8">
+      <c r="A29" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.8">
+      <c r="A30" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="92.4" x14ac:dyDescent="0.8">
+      <c r="A31" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A7DA874-34F7-4A30-A80C-E5AD3E9BD354}">
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr defaultRowHeight="23.1" x14ac:dyDescent="0.8"/>
+  <cols>
+    <col min="1" max="1" width="10.69921875" customWidth="1"/>
+    <col min="2" max="2" width="31.296875" customWidth="1"/>
+    <col min="3" max="3" width="16.6328125" customWidth="1"/>
+    <col min="4" max="4" width="23.09765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A1" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A2" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="7"/>
+    </row>
+    <row r="3" spans="1:4" ht="52.2" x14ac:dyDescent="0.8">
+      <c r="A3" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" s="7"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A4" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" s="7"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A5" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A6" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.8">
+      <c r="A7" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="104.4" x14ac:dyDescent="0.8">
+      <c r="A8" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A9" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" t="s">
+        <v>149</v>
+      </c>
+      <c r="D9" s="7"/>
+    </row>
+    <row r="10" spans="1:4" ht="30.6" x14ac:dyDescent="0.8">
+      <c r="A10" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="7"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A11" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A12" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D12" s="7"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A13" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A14" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+    </row>
+    <row r="15" spans="1:4" ht="30.6" x14ac:dyDescent="0.8">
+      <c r="A15" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" s="7"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A16" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" spans="1:4" ht="30.6" x14ac:dyDescent="0.8">
+      <c r="A17" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" spans="1:4" ht="30.6" x14ac:dyDescent="0.8">
+      <c r="A18" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" s="7"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A19" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" s="7"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A20" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" s="7"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A21" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A22" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A23" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A24" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+    </row>
+    <row r="25" spans="1:4" ht="30.6" x14ac:dyDescent="0.8">
+      <c r="A25" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D25" s="7"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A26" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A27" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="115.5" x14ac:dyDescent="0.8">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.8">
-      <c r="A15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="46.2" x14ac:dyDescent="0.8">
-      <c r="A16" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="92.4" x14ac:dyDescent="0.8">
-      <c r="A17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="69.3" x14ac:dyDescent="0.8">
-      <c r="A18" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="69.3" x14ac:dyDescent="0.8">
-      <c r="A19" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="46.2" x14ac:dyDescent="0.8">
-      <c r="A20" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="46.2" x14ac:dyDescent="0.8">
-      <c r="A21" t="s">
-        <v>77</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" t="s">
-        <v>18</v>
-      </c>
+      <c r="D27" s="7"/>
+    </row>
+    <row r="28" spans="1:4" ht="30.6" x14ac:dyDescent="0.8">
+      <c r="A28" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" s="7"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A29" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" s="8"/>
+      <c r="D29" s="7"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A30" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A31" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A32" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A33" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A34" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D35" s="7"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A36" s="7"/>
+      <c r="B36" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D36" s="7"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.8">
+      <c r="A37" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D37" s="7"/>
+    </row>
+    <row r="38" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.8">
+      <c r="A38" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D38" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/readme_file_information.xlsx
+++ b/readme_file_information.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleaw\Documents\PhD Fall 2021 - Spring 2022\dissertation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{037D94DF-3269-4900-88AE-35970BA87593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E722E81-E05D-4613-B11F-6C6F4D0B6970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{CBBF95AB-F81E-4FC2-8BBB-B7D3AC8BC92D}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{CBBF95AB-F81E-4FC2-8BBB-B7D3AC8BC92D}"/>
   </bookViews>
   <sheets>
     <sheet name="Files" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="196">
   <si>
     <t>File</t>
   </si>
@@ -139,9 +139,6 @@
   </si>
   <si>
     <t>make_panel_data.qmd</t>
-  </si>
-  <si>
-    <t>Filter for PINs with Flood Factor ≥ 5; analyze post-2023 PTAX-245 flood appeals; calculates AV changes in affected land blocks</t>
   </si>
   <si>
     <t>Parcel universe API, PTAX-245 appeal forms</t>
@@ -788,12 +785,87 @@
   <si>
     <t>Implied density tests of distributional parallel trends. Saves model and plot output because it takes a long time to run.</t>
   </si>
+  <si>
+    <t>only good for effective FIRM dates and uses FIRM panel shapes from before the NW Cook County FIRM updatewhere FIRMs were split</t>
+  </si>
+  <si>
+    <t>q1_assumption_tests.qmd</t>
+  </si>
+  <si>
+    <t>Question1_continued_staggered.qmd</t>
+  </si>
+  <si>
+    <t>Compares Fixed Effects models for question 1 to fixest::sunab() estimates. Creates staggered treatment plots and staggered model estimates for Question 1.</t>
+  </si>
+  <si>
+    <t>Analysis</t>
+  </si>
+  <si>
+    <t>NOT USED 11/23/2025: use `did` packageto by Callaway &amp; Sant'Anna but didn't do treatment within the cohorts. Instead it just compared pre and post event  trends of the cohorts, where it ran the models as if each cohort was treated.</t>
+  </si>
+  <si>
+    <t>comparison_2variables.R</t>
+  </si>
+  <si>
+    <t>comparison_3variables.R</t>
+  </si>
+  <si>
+    <t>splits high_ff_score &amp; post variable</t>
+  </si>
+  <si>
+    <t>uses high_ff _post variable</t>
+  </si>
+  <si>
+    <t>df_prep_bldg_v2026_03.RDS</t>
+  </si>
+  <si>
+    <t>outputs/compared_by2variables.rds</t>
+  </si>
+  <si>
+    <t>outputs/compared_by3variables.rds</t>
+  </si>
+  <si>
+    <t>For dissertation</t>
+  </si>
+  <si>
+    <t>dropped - q3</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Background info / Intro</t>
+  </si>
+  <si>
+    <t>Filter for PINs with Flood Factor ≥ 5; analyze post-2023 PTAX-245 flood appeals; calculates AV changes in affected land blocks. Mapped berwyn and cicero</t>
+  </si>
+  <si>
+    <t>make_panel_data.qmd - ARCHIVED</t>
+  </si>
+  <si>
+    <t>Y - Q2 prep</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Y - Q2</t>
+  </si>
+  <si>
+    <t>Became targets pipeline?</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Y - Q2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="18"/>
       <color theme="1"/>
@@ -845,6 +917,11 @@
       <sz val="12"/>
       <color rgb="FF212529"/>
       <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -904,7 +981,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="13">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1065,6 +1145,9 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1106,34 +1189,36 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FEF62D60-AD25-4B9B-92F2-6BD027E8C017}" name="Table2" displayName="Table2" ref="A1:F31" totalsRowShown="0" headerRowDxfId="10">
-  <autoFilter ref="A1:F31" xr:uid="{FEF62D60-AD25-4B9B-92F2-6BD027E8C017}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FEF62D60-AD25-4B9B-92F2-6BD027E8C017}" name="Table2" displayName="Table2" ref="A1:H35" totalsRowShown="0" headerRowDxfId="12">
+  <autoFilter ref="A1:H35" xr:uid="{FEF62D60-AD25-4B9B-92F2-6BD027E8C017}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E23">
     <sortCondition ref="A1:A23"/>
   </sortState>
-  <tableColumns count="6">
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{67B093ED-B042-42AF-828B-0E3979AEE20D}" name="File"/>
-    <tableColumn id="2" xr3:uid="{2469F763-8CD9-4F9B-81C9-081F0416F7A5}" name="Purpose" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{43956458-8468-4B36-9A02-0003207D1AF5}" name="Inputs" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{7920B79F-C2A1-4A94-A4C1-4C2F4CD3CC3B}" name="Outputs" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{2469F763-8CD9-4F9B-81C9-081F0416F7A5}" name="Purpose" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{43956458-8468-4B36-9A02-0003207D1AF5}" name="Inputs" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{7920B79F-C2A1-4A94-A4C1-4C2F4CD3CC3B}" name="Outputs" dataDxfId="9"/>
     <tableColumn id="5" xr3:uid="{8998AB64-C713-4A46-ACAB-BE6621288648}" name="Analysis Step"/>
-    <tableColumn id="6" xr3:uid="{235814BD-1B80-4B94-B701-26874451ABA9}" name="DV Model Type" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{235814BD-1B80-4B94-B701-26874451ABA9}" name="DV Model Type" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{C87ADADD-93E2-4AED-8641-D0949B073BE0}" name="For dissertation" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{B7CE5047-79E5-48AE-8419-7971A2C72023}" name="Became targets pipeline?" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{59E3DA47-3C97-48AE-8BE5-10905542AA94}" name="Table3" displayName="Table3" ref="A1:D38" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{59E3DA47-3C97-48AE-8BE5-10905542AA94}" name="Table3" displayName="Table3" ref="A1:D38" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A1:D38" xr:uid="{59E3DA47-3C97-48AE-8BE5-10905542AA94}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C34">
     <sortCondition ref="B1:B34"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="3" xr3:uid="{AC962285-503A-4963-A003-05FA381B10C7}" name="File Path" dataDxfId="4"/>
-    <tableColumn id="1" xr3:uid="{B777D240-3778-451E-A05B-8D2528E4BD53}" name="Output" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{168B95B9-E677-4740-9CB5-0E8DE4E5D63D}" name="Created By" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{BCBBA88B-69AC-4622-A217-558B80AFF3B1}" name="Column1" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{AC962285-503A-4963-A003-05FA381B10C7}" name="File Path" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{B777D240-3778-451E-A05B-8D2528E4BD53}" name="Output" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{168B95B9-E677-4740-9CB5-0E8DE4E5D63D}" name="Created By" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{BCBBA88B-69AC-4622-A217-558B80AFF3B1}" name="Column1" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1456,10 +1541,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F477E64-1C4D-4E5A-ADA3-AF3D9C88449B}">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultColWidth="23" defaultRowHeight="23.1" x14ac:dyDescent="0.8"/>
   <cols>
-    <col min="1" max="1" width="28.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="44.296875" style="4" customWidth="1"/>
     <col min="2" max="2" width="43" style="4" customWidth="1"/>
     <col min="3" max="3" width="28.69921875" style="4" customWidth="1"/>
     <col min="4" max="4" width="28.765625" style="4" customWidth="1"/>
@@ -1467,7 +1552,7 @@
     <col min="6" max="16384" width="23" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1481,50 +1566,62 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="46.2" x14ac:dyDescent="0.8">
+        <v>162</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="46.2" x14ac:dyDescent="0.8">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="E2" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="161.69999999999999" x14ac:dyDescent="0.8">
+        <v>163</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="161.69999999999999" x14ac:dyDescent="0.8">
       <c r="A3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="E3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="66.900000000000006" x14ac:dyDescent="0.8">
+      <c r="G3" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="66.900000000000006" x14ac:dyDescent="0.8">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -1532,7 +1629,7 @@
         <v>31</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>32</v>
@@ -1540,16 +1637,19 @@
       <c r="E4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="87" x14ac:dyDescent="0.8">
+      <c r="G4" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="87" x14ac:dyDescent="0.8">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>18</v>
@@ -1557,33 +1657,39 @@
       <c r="E5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="138.6" x14ac:dyDescent="0.8">
+      <c r="G5" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="138.6" x14ac:dyDescent="0.8">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>161</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>162</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="138.6" x14ac:dyDescent="0.8">
+      <c r="G6" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="138.6" x14ac:dyDescent="0.8">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>20</v>
@@ -1591,8 +1697,11 @@
       <c r="E7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="113.1" x14ac:dyDescent="0.8">
+      <c r="G7" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="113.1" x14ac:dyDescent="0.8">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1600,7 +1709,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>23</v>
@@ -1609,60 +1718,72 @@
         <v>16</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="46.2" x14ac:dyDescent="0.8">
+        <v>164</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="46.2" x14ac:dyDescent="0.8">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="E9" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="115.5" x14ac:dyDescent="0.8">
+      <c r="G9" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="115.5" x14ac:dyDescent="0.8">
       <c r="A10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="E10" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="46.2" x14ac:dyDescent="0.8">
+      <c r="H10" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="46.2" x14ac:dyDescent="0.8">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="69.3" x14ac:dyDescent="0.8">
+      <c r="G11" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="69.3" x14ac:dyDescent="0.8">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>13</v>
@@ -1676,104 +1797,128 @@
       <c r="E12" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="69.3" x14ac:dyDescent="0.8">
+      <c r="G12" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="69.3" x14ac:dyDescent="0.8">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>39</v>
       </c>
       <c r="E13" t="s">
         <v>16</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="69.3" x14ac:dyDescent="0.8">
+        <v>163</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="92.4" x14ac:dyDescent="0.8">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="E14" t="s">
         <v>16</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="115.5" x14ac:dyDescent="0.8">
+        <v>163</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="115.5" x14ac:dyDescent="0.8">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>190</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="E15" t="s">
         <v>24</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="46.2" x14ac:dyDescent="0.8">
+        <v>163</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="46.2" x14ac:dyDescent="0.8">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="E16" t="s">
         <v>16</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="115.5" x14ac:dyDescent="0.8">
+        <v>164</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="115.5" x14ac:dyDescent="0.8">
       <c r="A17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>88</v>
       </c>
       <c r="E17" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="66.900000000000006" x14ac:dyDescent="0.8">
+      <c r="G17" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="66.900000000000006" x14ac:dyDescent="0.8">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>4</v>
@@ -1782,35 +1927,41 @@
         <v>5</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E18" t="s">
         <v>24</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="69.3" x14ac:dyDescent="0.8">
+        <v>163</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="69.3" x14ac:dyDescent="0.8">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E19" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="66.900000000000006" x14ac:dyDescent="0.8">
+      <c r="G19" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="66.900000000000006" x14ac:dyDescent="0.8">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>28</v>
@@ -1819,15 +1970,18 @@
         <v>29</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E20" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="66.900000000000006" x14ac:dyDescent="0.8">
+      <c r="G20" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="66.900000000000006" x14ac:dyDescent="0.8">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>26</v>
@@ -1836,13 +1990,16 @@
         <v>27</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E21" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="46.2" x14ac:dyDescent="0.8">
+      <c r="G21" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="46.2" x14ac:dyDescent="0.8">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1853,13 +2010,16 @@
         <v>8</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E22" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="138.6" x14ac:dyDescent="0.8">
+      <c r="H22" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="138.6" x14ac:dyDescent="0.8">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -1867,7 +2027,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>12</v>
@@ -1875,93 +2035,174 @@
       <c r="E23" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="46.2" x14ac:dyDescent="0.8">
+      <c r="H23" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="46.2" x14ac:dyDescent="0.8">
       <c r="A24" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="C24" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="69.3" x14ac:dyDescent="0.8">
+      <c r="G24" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="69.3" x14ac:dyDescent="0.8">
       <c r="A25" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>155</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.8">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.8">
       <c r="A26" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.8">
+      <c r="A27" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.8">
-      <c r="A27" s="4" t="s">
+      <c r="E27" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.8">
+      <c r="A28" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.8">
-      <c r="A28" s="4" t="s">
+    <row r="29" spans="1:8" ht="46.2" x14ac:dyDescent="0.8">
+      <c r="A29" s="4" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="46.2" x14ac:dyDescent="0.8">
-      <c r="A29" s="4" t="s">
+      <c r="C29" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.8">
+      <c r="G29" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.8">
       <c r="A30" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="92.4" x14ac:dyDescent="0.8">
+      <c r="A31" s="4" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="92.4" x14ac:dyDescent="0.8">
-      <c r="A31" s="4" t="s">
+      <c r="B31" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C31" s="4" t="s">
+      <c r="D31" s="4" t="s">
         <v>169</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>170</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="115.5" x14ac:dyDescent="0.8">
+      <c r="A32" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="92.4" x14ac:dyDescent="0.8">
+      <c r="A33" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="46.2" x14ac:dyDescent="0.8">
+      <c r="A34" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="46.2" x14ac:dyDescent="0.8">
+      <c r="A35" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -1982,262 +2223,262 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A1" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>99</v>
-      </c>
       <c r="D1" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A2" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:4" ht="52.2" x14ac:dyDescent="0.8">
       <c r="A3" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>125</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>126</v>
       </c>
       <c r="D3" s="7"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A4" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A5" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A6" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.8">
       <c r="A7" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="104.4" x14ac:dyDescent="0.8">
       <c r="A8" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A9" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D9" s="7"/>
     </row>
     <row r="10" spans="1:4" ht="30.6" x14ac:dyDescent="0.8">
       <c r="A10" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A11" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A12" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D12" s="7"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A13" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A14" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:4" ht="30.6" x14ac:dyDescent="0.8">
       <c r="A15" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D15" s="7"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A16" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" ht="30.6" x14ac:dyDescent="0.8">
       <c r="A17" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D17" s="7"/>
     </row>
     <row r="18" spans="1:4" ht="30.6" x14ac:dyDescent="0.8">
       <c r="A18" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D18" s="7"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A19" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>147</v>
-      </c>
       <c r="C19" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D19" s="7"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A20" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D20" s="7"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A21" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>121</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>122</v>
       </c>
       <c r="D21" s="7"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A22" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>6</v>
@@ -2246,179 +2487,183 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A23" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D23" s="7"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.8">
+    <row r="24" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.8">
       <c r="A24" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
+        <v>133</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="25" spans="1:4" ht="30.6" x14ac:dyDescent="0.8">
       <c r="A25" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D25" s="7"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A26" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A27" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D27" s="7"/>
     </row>
     <row r="28" spans="1:4" ht="30.6" x14ac:dyDescent="0.8">
       <c r="A28" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D28" s="7"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A29" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="7"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A30" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D30" s="7"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A31" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A32" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A33" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A34" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>33</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A35" s="7"/>
       <c r="B35" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D35" s="7"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A36" s="7"/>
       <c r="B36" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>140</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>141</v>
       </c>
       <c r="D36" s="7"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.8">
       <c r="A37" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B37" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C37" s="7" t="s">
         <v>143</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>144</v>
       </c>
       <c r="D37" s="7"/>
     </row>
     <row r="38" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.8">
       <c r="A38" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D38" s="7"/>
     </row>
